--- a/main/ig/StructureDefinition-MESObservationGlucose.xlsx
+++ b/main/ig/StructureDefinition-MESObservationGlucose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T14:10:46+00:00</t>
+    <t>2026-03-12T14:12:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -653,7 +653,7 @@
     <t>MesReasonForMeasurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.2.0}
 </t>
   </si>
   <si>
@@ -670,7 +670,7 @@
     <t>MesMomentOfMeasurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-moment-of-measurement|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-moment-of-measurement|3.2.0}
 </t>
   </si>
   <si>
@@ -732,7 +732,7 @@
     <t>JDV-J157-MomentGlucose-ENS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J157-MomentGlucose-ENS/FHIR/JDV-J157-MomentGlucose-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J157-MomentGlucose-ENS/FHIR/JDV-J157-MomentGlucose-ENS|20250728120000</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -965,7 +965,7 @@
     <t>MesNumberOfDays</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-number-of-days|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-number-of-days|3.2.0}
 </t>
   </si>
   <si>
@@ -994,7 +994,7 @@
     <t>JDV_J164-GlucoseNumberOfDays-ENS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J164-GlucoseNumberOfDays-ENS/FHIR/JDV-J164-GlucoseNumberOfDays-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J164-GlucoseNumberOfDays-ENS/FHIR/JDV-J164-GlucoseNumberOfDays-ENS|20250728120000</t>
   </si>
   <si>
     <t>Observation.extension:MesDiabetisType</t>
@@ -1003,7 +1003,7 @@
     <t>MesDiabetisType</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-diabetis-type|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-diabetis-type|3.0.1}
 </t>
   </si>
   <si>
@@ -1283,7 +1283,7 @@
     <t>Glucose sanguin ou intersticiel</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J154-TypeGlucose-ENS/FHIR/JDV-J154-TypeGlucose-ENS|20250728120000</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1701,7 +1701,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J163-GlucoseUnits-ENS/FHIR/JDV-J163-GlucoseUnits-ENS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J163-GlucoseUnits-ENS/FHIR/JDV-J163-GlucoseUnits-ENS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J163-GlucoseUnits-ENS/FHIR/JDV-J163-GlucoseUnits-ENS|20240927120000</t>
   </si>
   <si>
     <t>Quantity.code</t>
@@ -1880,7 +1880,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/mesures/ValueSet/method-glucose-vs|3.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/mesures/ValueSet/method-glucose-vs|3.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -2117,7 +2117,7 @@
     <t>JDV_J148-ReferenceRangeAppliesTo-CISIS</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS|1.2.0</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J148-ReferenceRangeAppliesTo-CISIS/FHIR/JDV-J148-ReferenceRangeAppliesTo-CISIS|20250131120000</t>
   </si>
   <si>
     <t>Observation.referenceRange.appliesTo.id</t>
@@ -2677,7 +2677,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="100.9140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="110.9140625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-MESObservationGlucose.xlsx
+++ b/main/ig/StructureDefinition-MESObservationGlucose.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T14:12:24+00:00</t>
+    <t>2026-03-12T14:18:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
